--- a/网站内容_英文.xlsx
+++ b/网站内容_英文.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miaomiaojiang/PycharmProjects/dsy/venv/codex/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7152A0-A286-1142-8C68-1C6B2FD9A404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C4048F-B641-D04A-88B8-F9503BDA6032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-1360" windowWidth="38400" windowHeight="21000" xr2:uid="{F0E5AE36-DADF-684C-8E45-1043DE7F1EF9}"/>
+    <workbookView xWindow="-38400" yWindow="-1360" windowWidth="38400" windowHeight="21000" activeTab="3" xr2:uid="{F0E5AE36-DADF-684C-8E45-1043DE7F1EF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Homepage" sheetId="1" r:id="rId1"/>
@@ -42,15 +42,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
-    <t>\textbf{Siyu Duan}. Unraveling Linguistic Variations of Poetry Imagery with Interpretable Embedding by LLM. (forthcoming)</t>
-  </si>
-  <si>
-    <t>\textbf{Siyu Duan}, Jun Wang, Zhaopeng Wang, Qi Su. Quantifying Cultural DNA with Generative Large Language Model. (forthcoming)</t>
-  </si>
-  <si>
-    <t>\textbf{Siyu Duan}. \href{https://arxiv.org/abs/2510.27045}{Quantitative Intertextuality from the Digital Humanities Perspective: A Survey} (forthcoming)</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Jun Wang, \textbf{Siyu Duan*}, Binghao Fu, Liangcai Gao, Qi Su. \href{https://www.nature.com/articles/s41599-024-02763-6}{Evol Project: A Comprehensive Platform for Quantitative Analysis of Ancient Literature.} </t>
     </r>
@@ -526,15 +517,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Intertextuality Detection Results from Over 14 Million Core Chinese Classics (forthcoming)</t>
-  </si>
-  <si>
-    <t>Intertextuality Detection Results from Over One Billion Poems (forthcoming)</t>
-  </si>
-  <si>
-    <t>Support for Common Poetic Themes and Sentiment Polarity Classification (forthcoming)</t>
-  </si>
-  <si>
     <t>Publication</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -548,6 +530,30 @@
   </si>
   <si>
     <t>Student</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\textbf{Siyu Duan}. Unraveling Linguistic Variations of Poetry Imagery with Interpretable Embedding by LLM. (working paper)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\textbf{Siyu Duan}, Jun Wang, Zhaopeng Wang, Qi Su. Quantifying Cultural DNA with Generative Large Language Model. (under review)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\textbf{Siyu Duan}. \href{https://arxiv.org/abs/2510.27045}{Quantitative Intertextuality from the Digital Humanities Perspective: A Survey} (under review)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Over One Billion Intertextuality Detection Results from Classical Chinese Poems (coming soon)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Over 14 Million Intertextuality Detection Results from Core Chinese Classics (coming soon)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Support for Common Poetic Themes and Sentiment Polarity Classification (coming soon)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1004,102 +1010,102 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="D1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="112">
       <c r="A2" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="140">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="42">
       <c r="C4" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="98">
       <c r="A5" s="3"/>
       <c r="D5" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="70">
       <c r="D6" s="2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="56">
       <c r="D7" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="56">
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28">
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1120,35 +1126,35 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="409.6">
       <c r="A2" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1164,26 +1170,26 @@
   <sheetData>
     <row r="1" spans="1:2" ht="42">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="409.6">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1199,24 +1205,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/网站内容_英文.xlsx
+++ b/网站内容_英文.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miaomiaojiang/PycharmProjects/dsy/venv/codex/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE1AA7C-7D93-D64A-9371-24CC321DAB1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA411F7-5ED0-B54D-9BC4-88A6162D4C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{F0E5AE36-DADF-684C-8E45-1043DE7F1EF9}"/>
+    <workbookView xWindow="-38400" yWindow="-1960" windowWidth="38400" windowHeight="21600" xr2:uid="{F0E5AE36-DADF-684C-8E45-1043DE7F1EF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Homepage" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <r>
       <t xml:space="preserve">Jun Wang, \textbf{Siyu Duan*}, Binghao Fu, Liangcai Gao, Qi Su. \href{https://www.nature.com/articles/s41599-024-02763-6}{Evol Project: A Comprehensive Platform for Quantitative Analysis of Ancient Literature.} </t>
@@ -479,6 +479,10 @@
   </si>
   <si>
     <t>Large-scale Intertextuality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Undergraduate student: \href{https://wendie0219.github.io}{Jiwen Zhang}, \href{https://hui336.github.io/}{Ruyi Chen}, \href{https://lanq30721.github.io/}{Qiaozhi Lan}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -933,6 +937,7 @@
     <col min="4" max="4" width="52.5" customWidth="1"/>
     <col min="5" max="5" width="20.5" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="231.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -999,6 +1004,9 @@
       </c>
       <c r="F3" t="s">
         <v>35</v>
+      </c>
+      <c r="G3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="70">
